--- a/july 2026/LMT_JULY_26/Raheem/Raheem Store J Tower.xlsx
+++ b/july 2026/LMT_JULY_26/Raheem/Raheem Store J Tower.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E422BC9-37E1-4E9A-A1A8-D80B4BC6CCCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980FC937-5267-456A-9756-4E079B20CAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,6 +38,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'1'!$K$3:$P$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cust. Price List'!$A$7:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'1'!$A$1:$P$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -76,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="108">
   <si>
     <t>Gm</t>
   </si>
@@ -397,6 +398,9 @@
   </si>
   <si>
     <t>4920922-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address: J-Heights, Raiwind Rd, Lahore </t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1321,7 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2040,6 +2044,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3379,7 +3384,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -3407,7 +3412,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -4626,7 +4631,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -4654,7 +4659,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -5873,7 +5878,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -5901,7 +5906,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -7120,7 +7125,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -7148,7 +7153,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -8367,7 +8372,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -8395,7 +8400,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -9614,7 +9619,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -9642,7 +9647,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -10861,7 +10866,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -10889,7 +10894,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -12108,7 +12113,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -12136,7 +12141,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -13355,7 +13360,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -13383,7 +13388,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -14602,7 +14607,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -14630,7 +14635,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -18599,7 +18604,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -18627,7 +18632,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -19843,7 +19848,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -19871,7 +19876,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -21086,7 +21091,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -21114,7 +21119,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -22329,7 +22334,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -22357,7 +22362,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23577,7 +23582,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -23605,7 +23610,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23816,7 +23821,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>51858.655139399991</v>
+        <v>71211.360797099987</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23902,11 +23907,11 @@
       <c r="G16" s="113"/>
       <c r="H16" s="171">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16+'17'!H16+'18'!H16</f>
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>4197</v>
+        <v>10492.5</v>
       </c>
       <c r="J16" s="171">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
@@ -23914,27 +23919,27 @@
       </c>
       <c r="K16" s="171">
         <f>+'1'!K16+'2'!K16+'4'!K16+'3'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16</f>
-        <v>0</v>
+        <v>367.23750000000001</v>
       </c>
       <c r="L16" s="174">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>587.58000000000004</v>
+        <v>1468.95</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>3609.42</v>
+        <v>8656.3125</v>
       </c>
       <c r="N16" s="100">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>649.69560000000001</v>
+        <v>1558.13625</v>
       </c>
       <c r="O16" s="100">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>21.295578000000003</v>
+        <v>51.072243749999998</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>4280.4111780000003</v>
+        <v>10265.52099375</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="T16" s="162" t="str">
@@ -23976,11 +23981,11 @@
       <c r="G17" s="113"/>
       <c r="H17" s="171">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17+'17'!H17+'18'!H17</f>
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>4197</v>
+        <v>10492.5</v>
       </c>
       <c r="J17" s="171">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
@@ -23988,27 +23993,27 @@
       </c>
       <c r="K17" s="171">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
-        <v>0</v>
+        <v>367.23750000000001</v>
       </c>
       <c r="L17" s="174">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>587.58000000000004</v>
+        <v>1468.95</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>3609.42</v>
+        <v>8656.3125</v>
       </c>
       <c r="N17" s="100">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>649.69560000000001</v>
+        <v>1558.13625</v>
       </c>
       <c r="O17" s="100">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>21.295578000000003</v>
+        <v>51.072243749999998</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="0"/>
-        <v>4280.4111780000003</v>
+        <v>10265.52099375</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="162" t="str">
@@ -24050,11 +24055,11 @@
       <c r="G18" s="113"/>
       <c r="H18" s="171">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>10492.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="171">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
@@ -24066,23 +24071,23 @@
       </c>
       <c r="L18" s="174">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>1468.95</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="2"/>
-        <v>9023.5499999999993</v>
+        <v>0</v>
       </c>
       <c r="N18" s="100">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>1624.2389999999998</v>
+        <v>0</v>
       </c>
       <c r="O18" s="100">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>53.238944999999994</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="0"/>
-        <v>10701.027944999998</v>
+        <v>0</v>
       </c>
       <c r="T18" s="162" t="str">
         <f>+'5'!A5</f>
@@ -24120,11 +24125,11 @@
       <c r="G19" s="113"/>
       <c r="H19" s="171">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19</f>
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>8716.7999999999993</v>
+        <v>14528</v>
       </c>
       <c r="J19" s="171">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
@@ -24132,27 +24137,27 @@
       </c>
       <c r="K19" s="171">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
-        <v>0</v>
+        <v>508.48000000000008</v>
       </c>
       <c r="L19" s="174">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>1220.3520000000001</v>
+        <v>2033.9200000000003</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="2"/>
-        <v>7496.4479999999994</v>
+        <v>11985.6</v>
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>1349.3606399999999</v>
+        <v>2157.4079999999999</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>44.2290432</v>
+        <v>70.715040000000002</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>8890.0376832000002</v>
+        <v>14213.723039999999</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -24190,11 +24195,11 @@
       <c r="G20" s="113"/>
       <c r="H20" s="171">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20</f>
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>8716.7999999999993</v>
+        <v>14528</v>
       </c>
       <c r="J20" s="171">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
@@ -24202,27 +24207,27 @@
       </c>
       <c r="K20" s="171">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
-        <v>0</v>
+        <v>508.48000000000008</v>
       </c>
       <c r="L20" s="174">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>1220.3520000000001</v>
+        <v>2033.9200000000003</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="2"/>
-        <v>7496.4479999999994</v>
+        <v>11985.6</v>
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>1349.3606399999999</v>
+        <v>2157.4079999999999</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>44.2290432</v>
+        <v>70.715040000000002</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>8890.0376832000002</v>
+        <v>14213.723039999999</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -24272,7 +24277,7 @@
       </c>
       <c r="K21" s="171">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
-        <v>0</v>
+        <v>508.48000000000008</v>
       </c>
       <c r="L21" s="174">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
@@ -24280,19 +24285,19 @@
       </c>
       <c r="M21" s="117">
         <f t="shared" si="2"/>
-        <v>12494.08</v>
+        <v>11985.6</v>
       </c>
       <c r="N21" s="100">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>2248.9344000000001</v>
+        <v>2157.4079999999999</v>
       </c>
       <c r="O21" s="100">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>73.715072000000006</v>
+        <v>70.715040000000002</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="0"/>
-        <v>14816.729472000001</v>
+        <v>14213.723039999999</v>
       </c>
       <c r="T21" s="162" t="str">
         <f>+'8'!A5</f>
@@ -24330,11 +24335,11 @@
       <c r="G22" s="113"/>
       <c r="H22" s="171">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22+'17'!H22+'18'!H22</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7846.0000000000009</v>
       </c>
       <c r="J22" s="171">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22</f>
@@ -24342,27 +24347,27 @@
       </c>
       <c r="K22" s="171">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>0</v>
+        <v>674.75599999999997</v>
       </c>
       <c r="L22" s="174">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>0</v>
+        <v>392.30000000000007</v>
       </c>
       <c r="M22" s="117">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6778.9440000000004</v>
       </c>
       <c r="N22" s="100">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>0</v>
+        <v>1220.20992</v>
       </c>
       <c r="O22" s="100">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>0</v>
+        <v>39.995769600000003</v>
       </c>
       <c r="P22" s="119">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8039.1496896000008</v>
       </c>
       <c r="T22" s="162" t="str">
         <f>+'9'!A5</f>
@@ -24520,7 +24525,7 @@
       <c r="B25" s="211"/>
       <c r="C25" s="212">
         <f>H25/40</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D25" s="206"/>
       <c r="E25" s="206"/>
@@ -24531,11 +24536,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>50848.1</v>
+        <v>72415</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -24543,27 +24548,27 @@
       </c>
       <c r="K25" s="177">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2934.6710000000003</v>
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>7118.7340000000004</v>
+        <v>9431.9600000000009</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>43729.366000000002</v>
+        <v>60048.368999999999</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>7871.2858799999995</v>
+        <v>10808.706419999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>258.00325939999999</v>
+        <v>354.28537710000001</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>51858.655139399998</v>
+        <v>71211.360797099987</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24771,7 +24776,7 @@
       </c>
       <c r="U33" s="164">
         <f>SUM(U14:U28)</f>
-        <v>51858.655139399991</v>
+        <v>71211.360797099987</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24804,7 +24809,7 @@
       <c r="O35" s="223"/>
       <c r="P35" s="151">
         <f>I25</f>
-        <v>50848.1</v>
+        <v>72415</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24825,7 +24830,7 @@
       <c r="O36" s="225"/>
       <c r="P36" s="152">
         <f>L25</f>
-        <v>7118.7340000000004</v>
+        <v>9431.9600000000009</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24846,7 +24851,7 @@
       <c r="O37" s="225"/>
       <c r="P37" s="153">
         <f>K25</f>
-        <v>0</v>
+        <v>2934.6710000000003</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24868,7 +24873,7 @@
       <c r="O38" s="225"/>
       <c r="P38" s="152">
         <f>P35-P36-P37</f>
-        <v>43729.365999999995</v>
+        <v>60048.368999999999</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24893,7 +24898,7 @@
       </c>
       <c r="P39" s="152">
         <f>N25</f>
-        <v>7871.2858799999995</v>
+        <v>10808.706419999999</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24915,7 +24920,7 @@
       <c r="O40" s="227"/>
       <c r="P40" s="152">
         <f>P38+P39</f>
-        <v>51600.65187999999</v>
+        <v>70857.075419999994</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24940,7 +24945,7 @@
       </c>
       <c r="P41" s="152">
         <f>O41*P40</f>
-        <v>1290.0162969999999</v>
+        <v>1771.4268855</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24950,7 +24955,7 @@
       <c r="O42" s="205"/>
       <c r="P42" s="159">
         <f>P40+P41</f>
-        <v>52890.668176999992</v>
+        <v>72628.502305499991</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25063,7 +25068,7 @@
     <col min="8" max="8" width="5.453125" customWidth="1"/>
     <col min="9" max="9" width="11.54296875" customWidth="1"/>
     <col min="10" max="10" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="10" style="69" customWidth="1"/>
@@ -25122,7 +25127,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -25150,7 +25155,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -25159,7 +25164,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -25445,38 +25450,38 @@
       </c>
       <c r="G16" s="99"/>
       <c r="H16" s="100">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>4197</v>
+        <v>10492.5</v>
       </c>
       <c r="J16" s="102">
         <v>0</v>
       </c>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
-        <v>0</v>
+        <f>I16*3.5%</f>
+        <v>367.23750000000001</v>
       </c>
       <c r="L16" s="104">
         <f>I16*14%</f>
-        <v>587.58000000000004</v>
+        <v>1468.95</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>3609.42</v>
+        <v>8656.3125</v>
       </c>
       <c r="N16" s="105">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>649.69560000000001</v>
+        <v>1558.13625</v>
       </c>
       <c r="O16" s="106">
         <f t="shared" ref="O16:O24" si="1">(N16+M16)*$O$15</f>
-        <v>21.295578000000003</v>
+        <v>51.072243749999998</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="2">M16+N16+O16</f>
-        <v>4280.4111780000003</v>
+        <v>10265.52099375</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="XFD16" t="s">
@@ -25509,38 +25514,38 @@
       </c>
       <c r="G17" s="113"/>
       <c r="H17" s="114">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="3">(G17*D17)*F17+H17*F17</f>
-        <v>4197</v>
+        <v>10492.5</v>
       </c>
       <c r="J17" s="116">
         <v>0</v>
       </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="4">I17*$K$13</f>
-        <v>0</v>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="4">I17*3.5%</f>
+        <v>367.23750000000001</v>
       </c>
       <c r="L17" s="104">
         <f t="shared" ref="L17:L21" si="5">I17*14%</f>
-        <v>587.58000000000004</v>
+        <v>1468.95</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="6">I17-K17-L17</f>
-        <v>3609.42</v>
+        <v>8656.3125</v>
       </c>
       <c r="N17" s="117">
         <f t="shared" si="0"/>
-        <v>649.69560000000001</v>
+        <v>1558.13625</v>
       </c>
       <c r="O17" s="118">
         <f t="shared" si="1"/>
-        <v>21.295578000000003</v>
+        <v>51.072243749999998</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="2"/>
-        <v>4280.4111780000003</v>
+        <v>10265.52099375</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -25572,39 +25577,37 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>200</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="3"/>
-        <v>10492.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116">
         <v>0</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K18" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L18" s="104">
         <f t="shared" si="5"/>
-        <v>1468.95</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="6"/>
-        <v>9023.5499999999993</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>1624.2389999999998</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="1"/>
-        <v>53.238944999999994</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="2"/>
-        <v>10701.027944999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25633,38 +25636,38 @@
       </c>
       <c r="G19" s="113"/>
       <c r="H19" s="114">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I19" s="115">
         <f t="shared" si="3"/>
-        <v>8716.7999999999993</v>
+        <v>14528</v>
       </c>
       <c r="J19" s="116">
         <v>0</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="103">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>508.48000000000008</v>
       </c>
       <c r="L19" s="104">
         <f t="shared" si="5"/>
-        <v>1220.3520000000001</v>
+        <v>2033.9200000000003</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="6"/>
-        <v>7496.4479999999994</v>
+        <v>11985.6</v>
       </c>
       <c r="N19" s="117">
         <f t="shared" si="0"/>
-        <v>1349.3606399999999</v>
+        <v>2157.4079999999999</v>
       </c>
       <c r="O19" s="118">
         <f t="shared" si="1"/>
-        <v>44.2290432</v>
+        <v>70.715040000000002</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="2"/>
-        <v>8890.0376832000002</v>
+        <v>14213.723039999999</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25693,38 +25696,38 @@
       </c>
       <c r="G20" s="113"/>
       <c r="H20" s="114">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I20" s="115">
         <f t="shared" si="3"/>
-        <v>8716.7999999999993</v>
+        <v>14528</v>
       </c>
       <c r="J20" s="116">
         <v>0</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="103">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>508.48000000000008</v>
       </c>
       <c r="L20" s="104">
         <f t="shared" si="5"/>
-        <v>1220.3520000000001</v>
+        <v>2033.9200000000003</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="6"/>
-        <v>7496.4479999999994</v>
+        <v>11985.6</v>
       </c>
       <c r="N20" s="117">
         <f t="shared" si="0"/>
-        <v>1349.3606399999999</v>
+        <v>2157.4079999999999</v>
       </c>
       <c r="O20" s="118">
         <f t="shared" si="1"/>
-        <v>44.2290432</v>
+        <v>70.715040000000002</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="2"/>
-        <v>8890.0376832000002</v>
+        <v>14213.723039999999</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25762,9 +25765,9 @@
       <c r="J21" s="116">
         <v>0</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="103">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>508.48000000000008</v>
       </c>
       <c r="L21" s="104">
         <f t="shared" si="5"/>
@@ -25772,19 +25775,19 @@
       </c>
       <c r="M21" s="117">
         <f t="shared" si="6"/>
-        <v>12494.08</v>
+        <v>11985.6</v>
       </c>
       <c r="N21" s="117">
         <f t="shared" si="0"/>
-        <v>2248.9344000000001</v>
+        <v>2157.4079999999999</v>
       </c>
       <c r="O21" s="118">
         <f t="shared" si="1"/>
-        <v>73.715072000000006</v>
+        <v>70.715040000000002</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="2"/>
-        <v>14816.729472000001</v>
+        <v>14213.723039999999</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25812,35 +25815,37 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="113"/>
-      <c r="H22" s="114"/>
+      <c r="H22" s="114">
+        <v>200</v>
+      </c>
       <c r="I22" s="115">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7846.0000000000009</v>
       </c>
       <c r="J22" s="116"/>
       <c r="K22" s="1">
-        <f>I22*3.5%</f>
-        <v>0</v>
+        <f>I22*8.6%</f>
+        <v>674.75599999999997</v>
       </c>
       <c r="L22" s="119">
         <f>I22*5%</f>
-        <v>0</v>
+        <v>392.30000000000007</v>
       </c>
       <c r="M22" s="117">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6778.9440000000004</v>
       </c>
       <c r="N22" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1220.20992</v>
       </c>
       <c r="O22" s="118">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>39.995769600000003</v>
       </c>
       <c r="P22" s="119">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8039.1496896000008</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25970,11 +25975,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>50848.1</v>
+        <v>72415</v>
       </c>
       <c r="J25" s="182">
         <f>SUM(J16:J21)</f>
@@ -25982,28 +25987,29 @@
       </c>
       <c r="K25" s="138">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2934.6710000000003</v>
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>7118.7340000000004</v>
+        <v>9431.9600000000009</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>43729.366000000002</v>
+        <v>60048.368999999999</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>7871.2858799999995</v>
+        <v>10808.706419999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>258.00325939999999</v>
+        <v>354.28537710000001</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>51858.655139399998</v>
-      </c>
+        <v>71211.360797099987</v>
+      </c>
+      <c r="S25" s="254"/>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
       <c r="A26" s="144"/>
@@ -26052,7 +26058,7 @@
       <c r="O28" s="223"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>50848.1</v>
+        <v>72415</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26073,7 +26079,7 @@
       <c r="O29" s="225"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>7118.7340000000004</v>
+        <v>9431.9600000000009</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26094,7 +26100,7 @@
       <c r="O30" s="225"/>
       <c r="P30" s="153">
         <f>K25</f>
-        <v>0</v>
+        <v>2934.6710000000003</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26116,7 +26122,7 @@
       <c r="O31" s="225"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>43729.365999999995</v>
+        <v>60048.368999999999</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26141,7 +26147,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>7871.2858799999995</v>
+        <v>10808.706419999999</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26163,7 +26169,7 @@
       <c r="O33" s="227"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>51600.65187999999</v>
+        <v>70857.075419999994</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26188,7 +26194,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>258.00325939999993</v>
+        <v>354.28537709999995</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26198,7 +26204,7 @@
       <c r="O35" s="205"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>51858.655139399991</v>
+        <v>71211.360797099987</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26278,7 +26284,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup scale="83" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -26370,7 +26376,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -26398,7 +26404,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -27617,7 +27623,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -27645,7 +27651,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -28863,7 +28869,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -28891,7 +28897,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -30110,7 +30116,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -30138,7 +30144,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -31358,7 +31364,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -31386,7 +31392,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
